--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-diagnostico-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-diagnostico-urgencia.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/diagnostico-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/diagnostico-urgencia</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -268,7 +268,7 @@
 </t>
   </si>
   <si>
-    <t>Detailed information about conditions, problems or diagnoses</t>
+    <t>Hipótesis o diagnóstico de egreso de urgencia</t>
   </si>
   <si>
     <t>A clinical condition, problem, diagnosis, or other event, situation, issue, or clinical concept that has risen to a level of concern.</t>
@@ -441,7 +441,7 @@
 </t>
   </si>
   <si>
-    <t>Extension</t>
+    <t>Diagnóstico GES</t>
   </si>
   <si>
     <t>An Extension</t>
@@ -467,11 +467,8 @@
     <t>ges</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/diagnostico-ges}
+    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/diagnostico-ges}
 </t>
-  </si>
-  <si>
-    <t>Diagnóstico GES</t>
   </si>
   <si>
     <t>Indica si el diagnóstico corresponde a un problema de salud con Garantías Explícitas en Salud (GES).</t>
@@ -633,7 +630,7 @@
     <t>Condition.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>Sistema de identificadores de diagnósticos del establecimiento</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -660,7 +657,7 @@
     <t>Condition.identifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
+    <t>Identificador del diagnóstico</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -875,7 +872,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/ValueSet/vs-diagnostico-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-diagnostico-urgencia</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -918,7 +915,7 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
+    <t>Código CIE-10 o SNOMED CT</t>
   </si>
   <si>
     <t>A reference to a code defined by a terminology system.</t>
@@ -942,7 +939,7 @@
     <t>Condition.code.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
+    <t>Diagnóstico en texto, tal como lo registró el profesional</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1002,6 +999,9 @@
   <si>
     <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/nid/StructureDefinition/MINSALPaciente)
 </t>
+  </si>
+  <si>
+    <t>Paciente</t>
   </si>
   <si>
     <t>Paciente sobre al que corresponde la condición.</t>
@@ -1108,11 +1108,11 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/encuentro-urgencia)
+    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/encuentro-urgencia)
 </t>
   </si>
   <si>
-    <t>Encounter created as part of</t>
+    <t>Episodio de urgencia</t>
   </si>
   <si>
     <t>The Encounter during which this Condition was created or to which the creation of this record is tightly associated.</t>
@@ -1194,7 +1194,7 @@
 </t>
   </si>
   <si>
-    <t>Date record was first recorded</t>
+    <t>Fecha y hora de registro del diagnóstico</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
@@ -1216,7 +1216,7 @@
 </t>
   </si>
   <si>
-    <t>Who recorded the condition</t>
+    <t>Profesional que registra el diagnóstico</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -1767,7 +1767,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="82.85546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.58203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1782,7 +1782,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.90234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.75" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -2913,10 +2913,10 @@
         <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2976,7 +2976,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3002,14 +3002,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3031,16 +3031,16 @@
         <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>79</v>
@@ -3089,7 +3089,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3150,19 +3150,19 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>79</v>
@@ -3211,7 +3211,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3226,19 +3226,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>79</v>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3272,13 +3272,13 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3329,7 +3329,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3353,7 +3353,7 @@
         <v>79</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3364,14 +3364,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3393,13 +3393,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="N14" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3440,7 +3440,7 @@
         <v>139</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>79</v>
@@ -3449,7 +3449,7 @@
         <v>140</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3473,7 +3473,7 @@
         <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3484,10 +3484,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3513,16 +3513,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3547,31 +3547,31 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3595,7 +3595,7 @@
         <v>134</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3632,19 +3632,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
@@ -3669,31 +3669,31 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3714,10 +3714,10 @@
         <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>79</v>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3757,16 +3757,16 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3779,43 +3779,43 @@
         <v>79</v>
       </c>
       <c r="T17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3836,10 +3836,10 @@
         <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3876,16 +3876,16 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3899,43 +3899,43 @@
         <v>79</v>
       </c>
       <c r="T18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3956,10 +3956,10 @@
         <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -3970,10 +3970,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3996,13 +3996,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4053,7 +4053,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4074,10 +4074,10 @@
         <v>79</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4114,16 +4114,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4173,7 +4173,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4194,10 +4194,10 @@
         <v>79</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4234,16 +4234,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4269,14 +4269,14 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="Z21" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>234</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4302,25 +4302,25 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4354,16 +4354,16 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4389,13 +4389,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4413,7 +4413,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4422,36 +4422,36 @@
         <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>250</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4474,16 +4474,16 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4509,13 +4509,13 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4533,7 +4533,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4551,16 +4551,16 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4594,16 +4594,16 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4632,10 +4632,10 @@
         <v>115</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4653,7 +4653,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4671,31 +4671,31 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>269</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4714,19 +4714,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4773,7 +4773,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4788,30 +4788,30 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4834,13 +4834,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4891,7 +4891,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4915,7 +4915,7 @@
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4926,14 +4926,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4955,13 +4955,13 @@
         <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="N27" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5002,7 +5002,7 @@
         <v>139</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>79</v>
@@ -5011,7 +5011,7 @@
         <v>140</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5035,7 +5035,7 @@
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5046,10 +5046,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5072,19 +5072,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5133,7 +5133,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5154,10 +5154,10 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5194,19 +5194,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5255,7 +5255,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5276,10 +5276,10 @@
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5316,16 +5316,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5351,14 +5351,14 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="Y30" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="Y30" t="s" s="2">
+      <c r="Z30" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>308</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5393,31 +5393,31 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5436,10 +5436,10 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>315</v>
@@ -5495,7 +5495,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>91</v>
@@ -5556,13 +5556,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5613,7 +5613,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5637,7 +5637,7 @@
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5677,13 +5677,13 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="N33" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5724,7 +5724,7 @@
         <v>139</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
@@ -5733,7 +5733,7 @@
         <v>140</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5757,7 +5757,7 @@
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5794,7 +5794,7 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>324</v>
@@ -5949,7 +5949,7 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Y35" t="s" s="2">
         <v>333</v>
@@ -6034,7 +6034,7 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>337</v>
@@ -6154,7 +6154,7 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>343</v>
@@ -7106,13 +7106,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7163,7 +7163,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7187,7 +7187,7 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7227,13 +7227,13 @@
         <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="N46" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7283,7 +7283,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7307,7 +7307,7 @@
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7353,10 +7353,10 @@
         <v>404</v>
       </c>
       <c r="N47" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O47" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7466,7 +7466,7 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>407</v>
@@ -7499,7 +7499,7 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Y48" t="s" s="2">
         <v>409</v>
@@ -7544,10 +7544,10 @@
         <v>412</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7702,7 +7702,7 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>419</v>
@@ -7735,7 +7735,7 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Y50" t="s" s="2">
         <v>421</v>
@@ -7940,13 +7940,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7997,7 +7997,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8021,7 +8021,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8061,13 +8061,13 @@
         <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8117,7 +8117,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8141,7 +8141,7 @@
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8187,10 +8187,10 @@
         <v>404</v>
       </c>
       <c r="N54" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8300,7 +8300,7 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>434</v>
@@ -8333,7 +8333,7 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Y55" t="s" s="2">
         <v>436</v>
@@ -8375,7 +8375,7 @@
         <v>439</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>

--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-diagnostico-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-diagnostico-urgencia.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Hipótesis o diagnóstico de egreso de la atención de urgencia. Basado en CoreDiagnosticoCl de CL-Core. El tipo de diagnóstico del CMBD (hipótesis, confirmado, descartado) se expresa con `verificationStatus`.</t>
+    <t>Hipótesis o diagnóstico de egreso de la atención de urgencia. Basado en CoreDiagnosticoCl de CL-Core. El tipo de diagnóstico del CMBD se expresa solo con `verificationStatus`: hipótesis = provisional, confirmado = confirmed. Los diagnósticos descartados no se informan. En el alta el diagnóstico debe venir codificado en CIE-10.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -335,13 +335,190 @@
 </t>
   </si>
   <si>
-    <t>Condition.implicitRules</t>
+    <t>Condition.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Condition.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Condition.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Condition.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Condition.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Condition.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Condition.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>R (restringido) si el episodio está restringido</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Condition.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Condition.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -437,28 +614,13 @@
     <t>Condition.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Diagnóstico GES</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.extension:ges</t>
@@ -481,10 +643,6 @@
     <t>Condition.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -492,9 +650,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -532,35 +687,7 @@
     <t>Condition.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Condition.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Condition.identifier.use</t>
@@ -612,9 +739,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -766,7 +890,7 @@
     <t>Condition.verificationStatus</t>
   </si>
   <si>
-    <t>provisional (hipótesis) | confirmed (confirmado) | refuted (descartado)</t>
+    <t>provisional (hipótesis) | confirmed (confirmado)</t>
   </si>
   <si>
     <t>Estado de verificación de la condición o Diagnóstico</t>
@@ -776,7 +900,7 @@
 The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-ver-status</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-verificacion-diagnostico</t>
   </si>
   <si>
     <t>con-3
@@ -860,7 +984,7 @@
 </t>
   </si>
   <si>
-    <t>Diagnóstico: CIE-10 preferente; texto libre si no está codificado</t>
+    <t>Diagnóstico: CIE-10 obligatorio en el alta; la hipótesis del abandono puede ir solo en texto</t>
   </si>
   <si>
     <t>Identificación de la condición, el problema o el diagnóstico o registro del "problema ausente" o de los "problemas desconocidos".</t>
@@ -911,10 +1035,6 @@
     <t>Condition.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>Código CIE-10 o SNOMED CT</t>
   </si>
   <si>
@@ -970,9 +1090,6 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1108,11 +1225,11 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/encuentro-urgencia)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
-    <t>Episodio de urgencia</t>
+    <t>Episodio de urgencia (Encuentro de urgencia del mismo Bundle)</t>
   </si>
   <si>
     <t>The Encounter during which this Condition was created or to which the creation of this record is tightly associated.</t>
@@ -1754,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP57"/>
+  <dimension ref="A1:AP65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.07421875" customWidth="true" bestFit="true"/>
@@ -1767,7 +1884,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.58203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="85.265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1782,7 +1899,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.75" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.87890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -2306,10 +2423,10 @@
         <v>79</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>105</v>
@@ -2320,9 +2437,7 @@
       <c r="M5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>79</v>
@@ -2371,7 +2486,7 @@
         <v>79</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2383,7 +2498,7 @@
         <v>79</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>79</v>
@@ -2395,7 +2510,7 @@
         <v>79</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>79</v>
@@ -2413,14 +2528,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>79</v>
@@ -2432,16 +2547,16 @@
         <v>79</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2467,43 +2582,43 @@
         <v>79</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>79</v>
@@ -2515,7 +2630,7 @@
         <v>79</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>79</v>
@@ -2526,14 +2641,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2549,10 +2664,10 @@
         <v>79</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>122</v>
@@ -2635,7 +2750,7 @@
         <v>79</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>79</v>
@@ -2646,21 +2761,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>79</v>
@@ -2669,19 +2784,19 @@
         <v>79</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2731,19 +2846,19 @@
         <v>79</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>79</v>
@@ -2755,7 +2870,7 @@
         <v>79</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>79</v>
@@ -2766,10 +2881,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2780,7 +2895,7 @@
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>79</v>
@@ -2789,18 +2904,20 @@
         <v>79</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>79</v>
@@ -2837,29 +2954,31 @@
         <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>79</v>
@@ -2880,16 +2999,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>79</v>
       </c>
@@ -2898,27 +3015,29 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>79</v>
@@ -2967,7 +3086,7 @@
         <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2976,10 +3095,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>79</v>
@@ -3000,16 +3119,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3019,29 +3138,27 @@
         <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -3065,13 +3182,13 @@
         <v>79</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>79</v>
@@ -3089,7 +3206,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3101,7 +3218,7 @@
         <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>79</v>
@@ -3113,7 +3230,7 @@
         <v>79</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>79</v>
@@ -3122,12 +3239,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3135,13 +3252,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>79</v>
@@ -3150,20 +3267,18 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>160</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -3187,13 +3302,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -3211,7 +3326,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3226,7 +3341,7 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>79</v>
@@ -3235,10 +3350,10 @@
         <v>79</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>79</v>
@@ -3246,10 +3361,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3266,21 +3381,23 @@
         <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>79</v>
@@ -3329,7 +3446,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3341,7 +3458,7 @@
         <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>79</v>
@@ -3353,7 +3470,7 @@
         <v>79</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3364,21 +3481,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3390,16 +3507,16 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3425,28 +3542,28 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>174</v>
@@ -3455,13 +3572,13 @@
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>79</v>
@@ -3473,7 +3590,7 @@
         <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3491,7 +3608,7 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3504,26 +3621,24 @@
         <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
       </c>
@@ -3547,31 +3662,31 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3592,10 +3707,10 @@
         <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3606,21 +3721,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
@@ -3629,23 +3744,21 @@
         <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3669,69 +3782,69 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Y16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3739,35 +3852,31 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3779,7 +3888,7 @@
         <v>79</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>79</v>
@@ -3803,31 +3912,29 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>79</v>
@@ -3836,10 +3943,10 @@
         <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3850,18 +3957,20 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
@@ -3873,20 +3982,18 @@
         <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -3899,7 +4006,7 @@
         <v>79</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>79</v>
@@ -3935,19 +4042,19 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
@@ -3956,10 +4063,10 @@
         <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -3970,42 +4077,46 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -4053,19 +4164,19 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
@@ -4074,10 +4185,10 @@
         <v>79</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4086,12 +4197,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4099,13 +4210,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>79</v>
@@ -4114,18 +4225,20 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4173,13 +4286,13 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
@@ -4188,30 +4301,30 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4225,26 +4338,24 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>106</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4269,13 +4380,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -4293,7 +4404,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4302,68 +4413,68 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>238</v>
+        <v>109</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>113</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
+        <v>114</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>243</v>
+        <v>115</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4389,69 +4500,69 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>246</v>
+        <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>247</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>248</v>
+        <v>109</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4462,30 +4573,32 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4509,13 +4622,13 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4533,13 +4646,13 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
@@ -4551,16 +4664,16 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>255</v>
+        <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>258</v>
+        <v>79</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -4568,10 +4681,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4591,21 +4704,23 @@
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4629,13 +4744,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4653,7 +4768,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4671,31 +4786,31 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4714,19 +4829,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4739,7 +4854,7 @@
         <v>79</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>79</v>
@@ -4751,11 +4866,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>275</v>
+        <v>79</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4773,7 +4890,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4788,30 +4905,30 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4819,30 +4936,32 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4855,7 +4974,7 @@
         <v>79</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>79</v>
@@ -4891,7 +5010,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>168</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4903,7 +5022,7 @@
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
@@ -4912,10 +5031,10 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>79</v>
+        <v>251</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4926,21 +5045,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -4949,20 +5068,18 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>171</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -4999,31 +5116,31 @@
         <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>79</v>
@@ -5032,10 +5149,10 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>169</v>
+        <v>259</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5044,12 +5161,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5060,10 +5177,10 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>79</v>
@@ -5072,20 +5189,18 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5133,13 +5248,13 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
@@ -5154,10 +5269,10 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5168,10 +5283,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5179,7 +5294,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5188,26 +5303,24 @@
         <v>92</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5231,13 +5344,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5255,7 +5368,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5264,36 +5377,36 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5301,31 +5414,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5351,13 +5464,11 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5375,79 +5486,79 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>310</v>
+        <v>289</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>313</v>
+        <v>227</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5471,13 +5582,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5495,13 +5606,13 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>79</v>
@@ -5510,19 +5621,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -5530,10 +5641,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5556,15 +5667,17 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>166</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5589,13 +5702,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>79</v>
+        <v>303</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5613,7 +5726,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>168</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5625,67 +5738,69 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>169</v>
+        <v>306</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>307</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>149</v>
+        <v>310</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>136</v>
+        <v>227</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>171</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>172</v>
+        <v>312</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5709,69 +5824,67 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>79</v>
+        <v>315</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>79</v>
+        <v>317</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>169</v>
+        <v>319</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5785,26 +5898,24 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>106</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5853,7 +5964,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>108</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5862,10 +5973,10 @@
         <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
@@ -5877,7 +5988,7 @@
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5888,21 +5999,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
@@ -5911,19 +6022,19 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>113</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>114</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>115</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5949,43 +6060,43 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>333</v>
+        <v>79</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>334</v>
+        <v>79</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>335</v>
+        <v>119</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
@@ -5997,7 +6108,7 @@
         <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -6006,12 +6117,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6022,10 +6133,10 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
@@ -6034,18 +6145,20 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6093,13 +6206,13 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
@@ -6114,10 +6227,10 @@
         <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6126,12 +6239,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6139,13 +6252,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>79</v>
@@ -6154,18 +6267,20 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
       </c>
@@ -6213,7 +6328,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6234,10 +6349,10 @@
         <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>134</v>
+        <v>339</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6246,12 +6361,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6259,13 +6374,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
@@ -6274,16 +6389,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>348</v>
+        <v>227</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6309,13 +6424,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>79</v>
+        <v>344</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6333,13 +6448,13 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
@@ -6348,38 +6463,38 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>91</v>
@@ -6394,18 +6509,18 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
@@ -6453,10 +6568,10 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>91</v>
@@ -6468,19 +6583,19 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6488,10 +6603,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6514,17 +6629,15 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>366</v>
+        <v>105</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>367</v>
+        <v>106</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6573,7 +6686,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>365</v>
+        <v>108</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6582,10 +6695,10 @@
         <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
@@ -6597,52 +6710,54 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>371</v>
+        <v>109</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>374</v>
+        <v>112</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>113</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -6679,31 +6794,31 @@
         <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>119</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
@@ -6712,13 +6827,13 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -6726,10 +6841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6752,15 +6867,17 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>381</v>
+        <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6809,7 +6926,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6818,7 +6935,7 @@
         <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
@@ -6833,10 +6950,10 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>384</v>
+        <v>190</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -6844,10 +6961,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6870,15 +6987,17 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>387</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6903,13 +7022,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6927,7 +7046,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6948,13 +7067,13 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>391</v>
+        <v>190</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>392</v>
+        <v>79</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -6962,10 +7081,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6976,7 +7095,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -6985,18 +7104,20 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>394</v>
+        <v>206</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7045,19 +7166,19 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>397</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
@@ -7069,7 +7190,7 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7080,10 +7201,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7103,18 +7224,20 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>166</v>
+        <v>381</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7163,7 +7286,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>168</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7175,7 +7298,7 @@
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -7187,7 +7310,7 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7196,44 +7319,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>136</v>
+        <v>386</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>171</v>
+        <v>387</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>172</v>
+        <v>388</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>152</v>
+        <v>389</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7283,81 +7406,79 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>174</v>
+        <v>385</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>169</v>
+        <v>392</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>395</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7405,34 +7526,34 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>134</v>
+        <v>401</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -7440,10 +7561,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7466,15 +7587,17 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>186</v>
+        <v>404</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7499,13 +7622,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7523,7 +7646,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7532,7 +7655,7 @@
         <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
@@ -7541,27 +7664,27 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>279</v>
+        <v>409</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7572,25 +7695,25 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7641,16 +7764,16 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>103</v>
@@ -7662,19 +7785,19 @@
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AO49" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AP49" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>418</v>
       </c>
@@ -7693,22 +7816,22 @@
         <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>186</v>
+        <v>419</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7735,13 +7858,13 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>421</v>
+        <v>79</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -7783,10 +7906,10 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>79</v>
@@ -7808,7 +7931,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
@@ -7817,20 +7940,18 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N51" t="s" s="2">
         <v>427</v>
       </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7885,28 +8006,28 @@
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>429</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>79</v>
@@ -7914,10 +8035,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7928,7 +8049,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7940,13 +8061,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>165</v>
+        <v>432</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>166</v>
+        <v>433</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>167</v>
+        <v>434</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7997,19 +8118,19 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>168</v>
+        <v>431</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8021,7 +8142,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>169</v>
+        <v>436</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8032,21 +8153,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8058,17 +8179,15 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8117,19 +8236,19 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8141,7 +8260,7 @@
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8152,14 +8271,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>402</v>
+        <v>111</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8172,26 +8291,24 @@
         <v>79</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>403</v>
+        <v>113</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>404</v>
+        <v>114</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8239,7 +8356,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>405</v>
+        <v>119</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8251,7 +8368,7 @@
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8263,7 +8380,7 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8274,14 +8391,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>440</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8294,22 +8411,26 @@
         <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8333,13 +8454,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>436</v>
+        <v>79</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>437</v>
+        <v>79</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8357,7 +8478,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8366,25 +8487,25 @@
         <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>438</v>
+        <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>255</v>
+        <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>440</v>
+        <v>190</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>441</v>
+        <v>79</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>79</v>
@@ -8392,10 +8513,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8406,7 +8527,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8415,16 +8536,16 @@
         <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>443</v>
+        <v>227</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8451,13 +8572,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>448</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8475,16 +8596,16 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>103</v>
@@ -8493,16 +8614,16 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>79</v>
+        <v>450</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>417</v>
+        <v>319</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>441</v>
+        <v>79</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -8510,10 +8631,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8536,13 +8657,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8593,7 +8714,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8602,32 +8723,984 @@
         <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>79</v>
+        <v>449</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>450</v>
+        <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP57" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP57">
+  <autoFilter ref="A1:AP65">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8637,7 +9710,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
